--- a/daily_matches/job_matches_2026-03-08.xlsx
+++ b/daily_matches/job_matches_2026-03-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>AI-Driven Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -478,15 +478,15 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, LLaMA, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Data Lake, FastAPI</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, FAISS, Pinecone, ChromaDB, Prompt Engineering, TensorFlow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,14 +496,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c27bc0cbf92e5826</t>
+          <t>https://www.indeed.com/viewjob?jk=f0eb14a985ec302b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -513,15 +513,15 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>27.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, MLflow</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, FAISS, Pinecone, ChromaDB, Prompt Engineering, TensorFlow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c96ecafc624f15b3</t>
+          <t>https://www.indeed.com/viewjob?jk=dd36b3af081d974a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,15 +548,15 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, AKS, GitHub Actions, Terraform, Git</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, BigQuery, Data Lake, Dataflow, CI/CD, BigQuery</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67808ceb6c462dbc</t>
+          <t>https://www.indeed.com/viewjob?jk=29da198aaee83e0a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
+          <t>GenAI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python</t>
+          <t>AI Engineer, LangChain, RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, Keras, Git, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff508dfc11d64fe</t>
+          <t>https://www.indeed.com/viewjob?jk=9523c95c8a240349</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,15 +618,15 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, TensorFlow, PyTorch, S3, Glue, MLflow, CI/CD, Databricks, PySpark, Python</t>
+          <t>Redshift, Git, Snowflake, Databricks, Redshift, Kafka, Hadoop, MySQL, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a426fbf9b09b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=f225ad27d76e606c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Software Systems &amp; Data Engineer</t>
+          <t>AI-Driven Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Kinesis, CI/CD, Git, Databricks, PySpark, NoSQL, Tableau</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, AKS, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f045bd52323b67</t>
+          <t>https://www.indeed.com/viewjob?jk=2f88da9b8e7516ee</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Audacy, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, BigQuery, CI/CD, Terraform, Git, BigQuery, NoSQL, Python, SQL</t>
+          <t>AI Engineer, LangChain, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,137 +706,137 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31813beeef70938d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa431a0f71f59764</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Advanced Analyst II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Meijer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, TensorFlow, PyTorch, NLTK, Azure ML, Synapse, Git, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af4ddd4ed5ac47a5</t>
+          <t>https://www.indeed.com/viewjob?jk=9f3f529aa904b546</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Founding Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Naples, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Gemini, AWS SageMaker, Redshift, BigQuery, Kubernetes, Apache Airflow, Snowflake, Databricks, BigQuery</t>
+          <t>Gemini, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8710c024486747ff</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f5e6f4ef455fd4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Engineer - Innovation Lab</t>
+          <t>AI-Driven Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Zions Bancorporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, FastAPI, CI/CD, Git, Python, SQL, R</t>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2a11c31d8ce5293</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7cadb668678f16</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Cadmus Group, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Data Lake, CI/CD, Git, PySpark, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Pinecone, FastAPI, Kubernetes, CI/CD, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,49 +846,49 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9298a4309623a1a</t>
+          <t>https://www.indeed.com/viewjob?jk=6f5e99a2e7f39f10</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Celebration, FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, Git, Kafka, NoSQL, SQL, R, Java</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d14bdf995edae51e</t>
+          <t>https://www.indeed.com/viewjob?jk=bda711724fb96f94</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,15 +898,15 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Data Lake, Dataflow, BigQuery, Hadoop, Python, SQL, R, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07730b1f5d6d529d</t>
+          <t>https://www.indeed.com/viewjob?jk=6e96f791ed6e1185</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,15 +933,15 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, TensorFlow, PyTorch, PySpark, Matplotlib, Seaborn, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, Python, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfc6acb987d4792b</t>
+          <t>https://www.indeed.com/viewjob?jk=7a5d6190abb27508</t>
         </is>
       </c>
     </row>
@@ -968,15 +968,15 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
+          <t>Data Scientist, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, CI/CD, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,497 +986,77 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25db5000eeae2ce9</t>
+          <t>https://www.indeed.com/viewjob?jk=cfdbf463d4ec1494</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, AKS, Git, PostgreSQL, Python, SQL, R, Optimization</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Copilot, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0cf7aeb5a02166f</t>
+          <t>https://www.indeed.com/viewjob?jk=37f05dd4e98c67cd</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Java Production Support Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, Hadoop, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, S3, EC2, Docker, CI/CD, Terraform, Python, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=042d6a059fce02c7</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Summer 2026 Howard University Graduate Intern, Technology- Analytics Department</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>American Civil Liberties Union</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>York, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Polars, Matplotlib, Seaborn, Python, SQL, R, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bf14f91badbb5205</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Airwallex</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e2a37bf0f6749cc0</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Airwallex</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=42fc783bf719af43</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>North Carolina Department of Correction</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Data Scientist, Databricks, PySpark, Power BI, Matplotlib, Seaborn, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=661fbea1be1eba0d</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Founding Reliability &amp; Performance Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Kubernetes, AKS, Git, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ffe22ea463db3aa</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>AI Agent ML Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Bausch &amp; Lomb</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Wheeling, WV, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>LangChain, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7a53c4a08e7124</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>AI Agent ML Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Bausch &amp; Lomb</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Detroit, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>LangChain, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-01-27</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7715fd332eadbfc9</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>AI Agent ML Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Bausch &amp; Lomb</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>LangChain, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-01-27</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=de7e942c7c6cfc61</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>AI Agent ML Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Bausch &amp; Lomb</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Sacramento, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>LangChain, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-01-27</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e98f4a03ff74086</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>AI Agent ML Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Bausch &amp; Lomb</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>LangChain, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-01-27</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6c6167403dedf432</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Cloud DevSecOps Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>I4DM</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4af690cfdfaf9e78</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>GTM Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Seamless</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, PostgreSQL, Tableau, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b52470f59e76f94</t>
+          <t>https://www.indeed.com/viewjob?jk=9260483f5fd449bb</t>
         </is>
       </c>
     </row>
